--- a/artfynd/A 55178-2024 artfynd.xlsx
+++ b/artfynd/A 55178-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104058658</v>
+        <v>136776465</v>
       </c>
       <c r="B2" t="n">
-        <v>80298</v>
+        <v>79508</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>388</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Öster gällsjön, Mpd</t>
+          <t>Gällsjön, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546765</v>
+        <v>546654</v>
       </c>
       <c r="R2" t="n">
-        <v>6915881</v>
+        <v>6915929</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,22 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-10-11</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-10-11</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,66 +775,65 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104058658</t>
+          <t>https://artportalen.se/Sighting/136776465</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104058664</v>
+        <v>136776468</v>
       </c>
       <c r="B3" t="n">
-        <v>99118</v>
+        <v>83455</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Öster gällsjön, Mpd</t>
+          <t>Gällsjön, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546809</v>
+        <v>546721</v>
       </c>
       <c r="R3" t="n">
-        <v>6915820</v>
+        <v>6915923</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,22 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-10-11</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-10-11</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,49 +887,49 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104058664</t>
+          <t>https://artportalen.se/Sighting/136776468</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104058665</v>
+        <v>104058658</v>
       </c>
       <c r="B4" t="n">
-        <v>99118</v>
+        <v>80298</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>388</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546649</v>
+        <v>546765</v>
       </c>
       <c r="R4" t="n">
-        <v>6915941</v>
+        <v>6915881</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -977,7 +975,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +985,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,7 +1011,923 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/104058658</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136776466</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92111</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gällsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>546692</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6915902</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136776466</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136776463</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93409</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gällsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>546582</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6916028</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136776463</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136776470</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93409</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gällsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>546726</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6915942</v>
+      </c>
+      <c r="S7" t="n">
+        <v>8</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136776470</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136776467</v>
+      </c>
+      <c r="B8" t="n">
+        <v>83446</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Gällsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>546720</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6915923</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136776467</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136776469</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gällsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>546726</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6915916</v>
+      </c>
+      <c r="S9" t="n">
+        <v>6</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136776469</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>104058664</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Öster gällsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>546809</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6915820</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-10-11</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-10-11</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104058664</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>104058665</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Öster gällsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>546649</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6915941</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-10-11</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-10-11</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/104058665</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136776464</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99351</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gällsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>546649</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6915952</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136776464</t>
         </is>
       </c>
     </row>
@@ -1022,6 +1936,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55178-2024 artfynd.xlsx
+++ b/artfynd/A 55178-2024 artfynd.xlsx
@@ -1020,7 +1020,7 @@
         <v>136776466</v>
       </c>
       <c r="B5" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136776463</v>
       </c>
       <c r="B6" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136776470</v>
       </c>
       <c r="B7" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>136776464</v>
       </c>
       <c r="B12" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 55178-2024 artfynd.xlsx
+++ b/artfynd/A 55178-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136776465</v>
       </c>
       <c r="B2" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136776468</v>
       </c>
       <c r="B3" t="n">
-        <v>83455</v>
+        <v>83459</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136776466</v>
       </c>
       <c r="B5" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136776463</v>
       </c>
       <c r="B6" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136776470</v>
       </c>
       <c r="B7" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>136776467</v>
       </c>
       <c r="B8" t="n">
-        <v>83446</v>
+        <v>83450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>136776464</v>
       </c>
       <c r="B12" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 55178-2024 artfynd.xlsx
+++ b/artfynd/A 55178-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136776465</v>
       </c>
       <c r="B2" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136776468</v>
       </c>
       <c r="B3" t="n">
-        <v>83459</v>
+        <v>83461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136776466</v>
       </c>
       <c r="B5" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136776463</v>
       </c>
       <c r="B6" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136776470</v>
       </c>
       <c r="B7" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>136776467</v>
       </c>
       <c r="B8" t="n">
-        <v>83450</v>
+        <v>83452</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>136776464</v>
       </c>
       <c r="B12" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 55178-2024 artfynd.xlsx
+++ b/artfynd/A 55178-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136776465</v>
       </c>
       <c r="B2" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136776468</v>
       </c>
       <c r="B3" t="n">
-        <v>83461</v>
+        <v>83462</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136776466</v>
       </c>
       <c r="B5" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136776463</v>
       </c>
       <c r="B6" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136776470</v>
       </c>
       <c r="B7" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>136776467</v>
       </c>
       <c r="B8" t="n">
-        <v>83452</v>
+        <v>83453</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>136776464</v>
       </c>
       <c r="B12" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 55178-2024 artfynd.xlsx
+++ b/artfynd/A 55178-2024 artfynd.xlsx
@@ -1020,7 +1020,7 @@
         <v>136776466</v>
       </c>
       <c r="B5" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136776463</v>
       </c>
       <c r="B6" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136776470</v>
       </c>
       <c r="B7" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>136776464</v>
       </c>
       <c r="B12" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 55178-2024 artfynd.xlsx
+++ b/artfynd/A 55178-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136776465</v>
       </c>
       <c r="B2" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136776468</v>
       </c>
       <c r="B3" t="n">
-        <v>83462</v>
+        <v>83466</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136776466</v>
       </c>
       <c r="B5" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136776463</v>
       </c>
       <c r="B6" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136776470</v>
       </c>
       <c r="B7" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>136776467</v>
       </c>
       <c r="B8" t="n">
-        <v>83453</v>
+        <v>83457</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>136776464</v>
       </c>
       <c r="B12" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 55178-2024 artfynd.xlsx
+++ b/artfynd/A 55178-2024 artfynd.xlsx
@@ -1815,7 +1815,7 @@
         <v>136776464</v>
       </c>
       <c r="B12" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 55178-2024 artfynd.xlsx
+++ b/artfynd/A 55178-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136776465</v>
       </c>
       <c r="B2" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136776468</v>
       </c>
       <c r="B3" t="n">
-        <v>83466</v>
+        <v>83468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136776466</v>
       </c>
       <c r="B5" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136776463</v>
       </c>
       <c r="B6" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136776470</v>
       </c>
       <c r="B7" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>136776467</v>
       </c>
       <c r="B8" t="n">
-        <v>83457</v>
+        <v>83459</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>136776464</v>
       </c>
       <c r="B12" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 55178-2024 artfynd.xlsx
+++ b/artfynd/A 55178-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136776465</v>
       </c>
       <c r="B2" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136776468</v>
       </c>
       <c r="B3" t="n">
-        <v>83468</v>
+        <v>83481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136776466</v>
       </c>
       <c r="B5" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136776463</v>
       </c>
       <c r="B6" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136776470</v>
       </c>
       <c r="B7" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>136776467</v>
       </c>
       <c r="B8" t="n">
-        <v>83459</v>
+        <v>83472</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136776469</v>
       </c>
       <c r="B9" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>136776464</v>
       </c>
       <c r="B12" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 55178-2024 artfynd.xlsx
+++ b/artfynd/A 55178-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136776465</v>
       </c>
       <c r="B2" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136776468</v>
       </c>
       <c r="B3" t="n">
-        <v>83481</v>
+        <v>83483</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136776466</v>
       </c>
       <c r="B5" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136776463</v>
       </c>
       <c r="B6" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136776470</v>
       </c>
       <c r="B7" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>136776467</v>
       </c>
       <c r="B8" t="n">
-        <v>83472</v>
+        <v>83474</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136776469</v>
       </c>
       <c r="B9" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>136776464</v>
       </c>
       <c r="B12" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 55178-2024 artfynd.xlsx
+++ b/artfynd/A 55178-2024 artfynd.xlsx
@@ -1498,11 +1498,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gällsjön, Mpd</t>

--- a/artfynd/A 55178-2024 artfynd.xlsx
+++ b/artfynd/A 55178-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136776468</v>
       </c>
       <c r="B3" t="n">
-        <v>83483</v>
+        <v>83486</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136776466</v>
       </c>
       <c r="B5" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136776463</v>
       </c>
       <c r="B6" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136776470</v>
       </c>
       <c r="B7" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>136776467</v>
       </c>
       <c r="B8" t="n">
-        <v>83474</v>
+        <v>83477</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>136776464</v>
       </c>
       <c r="B12" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 55178-2024 artfynd.xlsx
+++ b/artfynd/A 55178-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136776465</v>
       </c>
       <c r="B2" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136776468</v>
       </c>
       <c r="B3" t="n">
-        <v>83486</v>
+        <v>83496</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136776466</v>
       </c>
       <c r="B5" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136776463</v>
       </c>
       <c r="B6" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136776470</v>
       </c>
       <c r="B7" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>136776467</v>
       </c>
       <c r="B8" t="n">
-        <v>83477</v>
+        <v>83487</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136776469</v>
       </c>
       <c r="B9" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>136776464</v>
       </c>
       <c r="B12" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 55178-2024 artfynd.xlsx
+++ b/artfynd/A 55178-2024 artfynd.xlsx
@@ -1020,7 +1020,7 @@
         <v>136776466</v>
       </c>
       <c r="B5" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136776463</v>
       </c>
       <c r="B6" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136776470</v>
       </c>
       <c r="B7" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>136776464</v>
       </c>
       <c r="B12" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 55178-2024 artfynd.xlsx
+++ b/artfynd/A 55178-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136776465</v>
       </c>
       <c r="B2" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136776468</v>
       </c>
       <c r="B3" t="n">
-        <v>83496</v>
+        <v>83499</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136776466</v>
       </c>
       <c r="B5" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136776463</v>
       </c>
       <c r="B6" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136776470</v>
       </c>
       <c r="B7" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>136776467</v>
       </c>
       <c r="B8" t="n">
-        <v>83487</v>
+        <v>83490</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136776469</v>
       </c>
       <c r="B9" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>136776464</v>
       </c>
       <c r="B12" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 55178-2024 artfynd.xlsx
+++ b/artfynd/A 55178-2024 artfynd.xlsx
@@ -1020,7 +1020,7 @@
         <v>136776466</v>
       </c>
       <c r="B5" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136776463</v>
       </c>
       <c r="B6" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136776470</v>
       </c>
       <c r="B7" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>136776464</v>
       </c>
       <c r="B12" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
